--- a/reporte_filtrado/reporte_filtrado.xlsx
+++ b/reporte_filtrado/reporte_filtrado.xlsx
@@ -413,19 +413,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>NOMBRE</t>
+          <t>Producto</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>VENTAS</t>
+          <t>Unnamed: 1</t>
         </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Unnamed: 2</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>1500</v>
       </c>
     </row>
   </sheetData>
